--- a/www/flightdata/xlsx/eoss-293.xlsx
+++ b/www/flightdata/xlsx/eoss-293.xlsx
@@ -3741,7 +3741,7 @@
         <v>28232.1</v>
       </c>
       <c r="I2">
-        <v>650</v>
+        <v>487</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
